--- a/evidence/pg16_recovery_process_restart_1.xlsx
+++ b/evidence/pg16_recovery_process_restart_1.xlsx
@@ -87,7 +87,7 @@
     <t>snapshot_id</t>
   </si>
   <si>
-    <t>1f2b2adb0a3b960ce7e7fe01f116342f</t>
+    <t>32b308b9d71b7807149489f37d9ccb42</t>
   </si>
   <si>
     <t>integration_id</t>
@@ -123,19 +123,19 @@
     <t>source_watermark</t>
   </si>
   <si>
-    <t>fixture-6e3e03ac3957cd6355248d768b047313</t>
+    <t>fixture-45461faf38548510c9cb1c7fd5b8e860</t>
   </si>
   <si>
     <t>source_snapshot_ref</t>
   </si>
   <si>
-    <t>5b0ed5986c93ff70abdd838fa754b956</t>
+    <t>31c8373ebab1d5f3ba5f1d0891fffb9a</t>
   </si>
   <si>
     <t>expires_at</t>
   </si>
   <si>
-    <t>2026-10-26T07:06:07Z</t>
+    <t>2026-10-26T07:30:20Z</t>
   </si>
   <si>
     <t>precision</t>
